--- a/Excel files/Employee Attrition Prediction.xlsx
+++ b/Excel files/Employee Attrition Prediction.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Student\Desktop\Pandas\Machine-Learning\Excel files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF3280B-D18B-40D2-9F55-889EDEE16F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2CEE30A-260C-4992-B47C-E54A787FE518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -3295,4 +3296,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67AA8EDA-8EB1-4297-B119-636A6D0983DD}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>